--- a/review_mapping_אחר.xlsx
+++ b/review_mapping_אחר.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G284"/>
+  <dimension ref="A1:G283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4500,319 +4500,317 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>בר קרן גמולים א' - מבטיח תשואה בשיעור 5.5 אחוז לשנה</t>
+          <t>אלפא מור קופת גמל לתגמולים ואישית לפיצויים וקופת גמל לא משלמת לקצבה אג"ח עד 25% במניות</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>משולב מניות</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>אג"ח ממשלתי</t>
+          <t>אג"ח עד 25% מניות</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="G125" t="n">
-        <v>192</v>
+        <v>51</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>הפניקס גמולה מבטיחת תשואה</t>
+          <t>אקסלנס השתלמות פאסיבי-מדדי אג"ח עד 25% במדדי מניות</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>משולב במניות - פאסיבי</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>אג"ח ממשלתי</t>
+          <t>אג"ח עד 25% מניות</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1.3</v>
+        <v>20.6</v>
       </c>
       <c r="G126" t="n">
-        <v>181</v>
+        <v>86</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>מיטב ביטחון מבטיח תשואה 4.5%</t>
+          <t>הלמן-אלדובי גמל אג"ח עד 25% במניות</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>משולב מניות</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>אג"ח ממשלתי</t>
+          <t>אג"ח עד 25% מניות</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G127" t="n">
-        <v>192</v>
+        <v>103</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>מיטב ביטחון מבטיח תשואה 5.5%</t>
+          <t>הלמן-אלדובי השתלמות אג"ח עד 25% במניות</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>משולב מניות</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>אג"ח ממשלתי</t>
+          <t>אג"ח עד 25% מניות</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>23.9</v>
       </c>
       <c r="G128" t="n">
-        <v>192</v>
+        <v>103</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>מנורה מבטחים אמיר מדד בגין</t>
+          <t>מיטב גמל אג"ח 85</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>אג"ח ממשלתי</t>
+          <t>אג"ח עד 25% מניות</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="G129" t="n">
-        <v>192</v>
+        <v>51</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>מנורה מבטחים אמיר מדד ידוע</t>
+          <t>מיטב גמל חכם מסלול 60 פלוס</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>אג"ח ממשלתי</t>
+          <t>אג"ח עד 25% מניות</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="G130" t="n">
-        <v>192</v>
+        <v>54</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>מנורה מבטחים יותר מסלול א'</t>
+          <t>מיטב דש גמל  אג"ח עד 25% במניות</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>משולב מניות</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>אג"ח ממשלתי</t>
+          <t>אג"ח עד 25% מניות</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>0</v>
-      </c>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>192</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>מנורה מבטחים יותר מסלול ב'</t>
+          <t>מיטב השתלמות אג"ח 85</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>אג"ח ממשלתי</t>
+          <t>אג"ח עד 25% מניות</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="G132" t="n">
-        <v>192</v>
+        <v>51</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>מנורה מבטחים יותר מסלול ג'</t>
+          <t>אגודה שיתופית של עובדי התעשיה האוירית לניהול קופות גמל בע"מ מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>מבטיח תשואה</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>אג"ח ממשלתי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G133" t="n">
-        <v>192</v>
+        <v>121</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>אלפא מור קופת גמל לתגמולים ואישית לפיצויים וקופת גמל לא משלמת לקצבה אג"ח עד 25% במניות</t>
+          <t>אי.בי.אי. לתגמולים ופיצויים מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>משולב מניות</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>אג"ח עד 25% מניות</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4821,31 +4819,31 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>23.4</v>
+        <v>42.3</v>
       </c>
       <c r="G134" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>אקסלנס השתלמות פאסיבי-מדדי אג"ח עד 25% במדדי מניות</t>
+          <t>איילון תגמולים ואישית לפיצויים מסלולית עד 50</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>משולב במניות - פאסיבי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>אג"ח עד 25% מניות</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4854,31 +4852,31 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>20.6</v>
+        <v>37.7</v>
       </c>
       <c r="G135" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>הלמן-אלדובי גמל אג"ח עד 25% במניות</t>
+          <t>אינפיניטי גמל מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>משולב מניות</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>אג"ח עד 25% מניות</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4887,31 +4885,31 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>24</v>
+        <v>50.9</v>
       </c>
       <c r="G136" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>הלמן-אלדובי השתלמות אג"ח עד 25% במניות</t>
+          <t>אלטשולר שחם גמל לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>משולב מניות</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>אג"ח עד 25% מניות</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4920,31 +4918,31 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>23.9</v>
+        <v>52.5</v>
       </c>
       <c r="G137" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>מיטב גמל אג"ח 85</t>
+          <t>אלטשולר שחם גמל לעמיתי חבר עד 50</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>אג"ח עד 25% מניות</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4953,31 +4951,31 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>12.8</v>
+        <v>53</v>
       </c>
       <c r="G138" t="n">
-        <v>51</v>
+        <v>122</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>מיטב גמל חכם מסלול 60 פלוס</t>
+          <t>אלפא מור קופת גמל לחיסכון, קופת גמל לתגמולים וקופת גמל אישית לפיצויים - לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>אג"ח עד 25% מניות</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4986,31 +4984,31 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>13.5</v>
+        <v>56.6</v>
       </c>
       <c r="G139" t="n">
-        <v>54</v>
+        <v>85</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>מיטב דש גמל  אג"ח עד 25% במניות</t>
+          <t>אנליסט מסלולית קופת גמל - מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>משולב מניות</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>אג"ח עד 25% מניות</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5018,30 +5016,32 @@
           <t>בינונית</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="n">
+        <v>53.9</v>
+      </c>
       <c r="G140" t="n">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>מיטב השתלמות אג"ח 85</t>
+          <t>ארם - קופת גמל לתגמולים של ארגון הרופאים עובדי המדינה עד 50</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>אג"ח עד 25% מניות</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5050,59 +5050,59 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>12.8</v>
+        <v>57.1</v>
       </c>
       <c r="G141" t="n">
-        <v>51</v>
+        <v>121</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>יונט השתלמות בניהול אישי</t>
+          <t>גמל-על, קופת תגמולים לעובדי אל על, אגודה שיתופית בע"מ עד 50</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>(ריק)</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>(ריק)</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>אחר, לבדיקה</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>לבדיקה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>13.3</v>
+        <v>54.3</v>
       </c>
       <c r="G142" t="n">
-        <v>38</v>
+        <v>122</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>הפניקס השתלמות - מסלול שיטת הפניקס</t>
+          <t>הילה - לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>קוהורטות</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>קוהורטות</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5116,26 +5116,26 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>33.2</v>
+        <v>46.7</v>
       </c>
       <c r="G143" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>הפניקס תגמולים ופיצויים- מסלול שיטת הפניקס</t>
+          <t>הלמן-אלדובי גמל מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>קוהורטות</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>קוהורטות</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5149,26 +5149,26 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>19.9</v>
+        <v>44</v>
       </c>
       <c r="G144" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>הראל השתלמות לטווח ארוך</t>
+          <t>הפניקס גמל לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>מתמחה אחר</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>אוכלוסיית יעד</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5182,26 +5182,26 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="G145" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>מיטב גמל חכם מסלול בין 50 ל-60</t>
+          <t>הפניקס גמל פאסיבי לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>אג"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5215,26 +5215,26 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>24.4</v>
+        <v>49.2</v>
       </c>
       <c r="G146" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>מיטב השתלמות מעל 6 שנות וותק</t>
+          <t>הפניקס השתלמות - מסלול שיטת הפניקס</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>מתמחה אחר</t>
+          <t>קוהורטות</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>אוכלוסיית יעד</t>
+          <t>קוהורטות</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5248,26 +5248,26 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>14.1</v>
+        <v>33.2</v>
       </c>
       <c r="G147" t="n">
-        <v>133</v>
+        <v>65</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>מנורה מבטחים השתלמות מסלול לטווח ארוך</t>
+          <t>הפניקס תגמולים ופיצויים - מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>מתמחה אחר</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>אוכלוסיית יעד</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5281,1293 +5281,1307 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>45</v>
+        <v>33.4</v>
       </c>
       <c r="G148" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>איילון השתלמות מסלול מט"ח</t>
+          <t>הפניקס תגמולים ופיצויים- מסלול שיטת הפניקס</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>קוהורטות</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>קוהורטות</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="G149" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>איילון השתלמות מסלול שקלי</t>
+          <t>הראל גמל לגילאי 50 ומטה</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>35.1</v>
       </c>
       <c r="G150" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>איילון לפיצויים מסלול מט"ח</t>
+          <t>הראל גמל מסלול לגילאי  50 ומטה</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>49.8</v>
+      </c>
       <c r="G151" t="n">
-        <v>4</v>
+        <v>121</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>איילון לפיצויים מסלול שקלי</t>
+          <t>הראל השתלמות לטווח ארוך</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מתמחה אחר</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>אוכלוסיית יעד</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr"/>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>50</v>
+      </c>
       <c r="G152" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>איילון תגמולים ואישית לפיצויים מסלול מט"ח</t>
+          <t>חברה לניהול קופות גמל של העובדים בעיריית תל - אביב יפו בע"מ עד 50</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>0</v>
-      </c>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>איילון תגמולים ואישית לפיצויים מסלול שקלי</t>
+          <t>ילין לפידות קופת גמל מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>52.5</v>
       </c>
       <c r="G154" t="n">
-        <v>42</v>
+        <v>121</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>אנליסט גמל מט"ח</t>
+          <t>כור-תדיראן קופת גמל אישית לתגמולים ולפיצויים עד 50</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="G155" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>אקסלנס אופיר - מסלול מט"ח טווח קצר</t>
+          <t>כלל תמר עד 50</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>מט"ח טווח קצר</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>48.1</v>
       </c>
       <c r="G156" t="n">
-        <v>13</v>
+        <v>122</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>אקסלנס גמל מט"ח</t>
+          <t>מגדל השתלמות מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מתמחה אחר</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>אוכלוסיית יעד</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>92.40000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="G157" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>אקסלנס גמל פלטינום שקלי</t>
+          <t>מגדל לתגמולים ולפיצויים מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>50.1</v>
       </c>
       <c r="G158" t="n">
-        <v>37</v>
+        <v>122</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>אקסלנס גמל שקלי</t>
+          <t>מור מנורה מבטחים מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>49.1</v>
       </c>
       <c r="G159" t="n">
-        <v>62</v>
+        <v>123</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>אקסלנס השתלמות מט"ח</t>
+          <t>מחוג  מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>48.4</v>
       </c>
       <c r="G160" t="n">
-        <v>62</v>
+        <v>121</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>אקסלנס השתלמות פלטינום שקלי</t>
+          <t>מיטב אגוד תגמולים עד 50</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F161" t="n">
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>37</v>
+        <v>105</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>אקסלנס השתלמותשקלי</t>
+          <t>מיטב גמל חכם מסלול בין 50 ל-60</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>אג"ח</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr"/>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>24.4</v>
+      </c>
       <c r="G162" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>אקסלנס משכית - מסלול מט"ח טווח קצר</t>
+          <t>מיטב גמל לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>מט"ח טווח קצר</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="G163" t="n">
-        <v>18</v>
+        <v>121</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>אקסלנס משכית - מסלול מט"חי</t>
+          <t>מיטב השתלמות מעל 6 שנות וותק</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מתמחה אחר</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>אוכלוסיית יעד</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="G164" t="n">
-        <v>37</v>
+        <v>133</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>אקסלנס עדי - מסלול מט"ח טווח קצר</t>
+          <t>מנורה מבטחים השתלמות מסלול לטווח ארוך</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מתמחה אחר</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>מט"ח טווח קצר</t>
+          <t>אוכלוסיית יעד</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G165" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>אקסלנס שחקים מסלול שקלי ב'</t>
+          <t>מנורה מבטחים תגמולים ופיצויים מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>48.6</v>
       </c>
       <c r="G166" t="n">
-        <v>13</v>
+        <v>123</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>אתגרים - מסלול שיקלי</t>
+          <t>סלייס גמל קופת גמל לחסכון מדרגות עד 50</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr"/>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>62.2</v>
+      </c>
       <c r="G167" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>אתגרים לפיצויים - מסלול שיקלי</t>
+          <t>עוצ"מ - אגודה שיתופית לניהול קופות גמל בע"מ - מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr"/>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>47.9</v>
+      </c>
       <c r="G168" t="n">
-        <v>4</v>
+        <v>123</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>הלמן-אלדובי בר-יציב שקלי</t>
+          <t>פסגות גדיש לבני 50  ומטה</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>45.2</v>
       </c>
       <c r="G169" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>הלמן-אלדובי השתלמות שקלי</t>
+          <t>קו הבריאות קופת גמל לתגמולים ולפיצויים (לא משלמת) לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>51.8</v>
       </c>
       <c r="G170" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>הפניקס מרכזית לפיצויים שקלי</t>
+          <t>קופת גמל אישית לפיצויים של העובדים בעיריית תל-אביב יפו - מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F171" t="n">
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>181</v>
+        <v>104</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>הראל גמל מסלול שקלי</t>
+          <t>קופת גמל גל לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="G172" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>הראל השתלמות מסלול שקלי</t>
+          <t>קופת גמל הגומל לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>49.2</v>
       </c>
       <c r="G173" t="n">
-        <v>115</v>
+        <v>75</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>הראל קמ"פ מסלול שקלי</t>
+          <t>קופת גמל הנדסאים - מסלול עד 50</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="G174" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>חיננית - מסלול מט"ח</t>
+          <t>קופת גמל כלנית לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>51.3</v>
       </c>
       <c r="G175" t="n">
-        <v>13</v>
+        <v>122</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>חיננית - מסלול שקלי</t>
+          <t>קופת גמל למשרתי הקבע בצה"ל קופת גמל לא משלמת לקצבה עד 50</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="G176" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>כלל גמל מט"ח</t>
+          <t>קופת גמל מחר לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>41.2</v>
+      </c>
       <c r="G177" t="n">
-        <v>4</v>
+        <v>122</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>כלל גמל שקלי</t>
+          <t>קופת גמל עו"ס לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr"/>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>48.6</v>
+      </c>
       <c r="G178" t="n">
-        <v>4</v>
+        <v>122</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>כלל השתלמות מט"ח</t>
+          <t>קופת גמל עמ"י מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr"/>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>50.9</v>
+      </c>
       <c r="G179" t="n">
-        <v>74</v>
+        <v>121</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>כלל השתלמות שקלים</t>
+          <t>קופת גמל שדות לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr"/>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>43.5</v>
+      </c>
       <c r="G180" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>כלל תמר מט"ח</t>
+          <t>קופת התגמולים לעובדי בנק דיסקונט לבני  50 ומטה</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>0.9</v>
+        <v>58</v>
       </c>
       <c r="G181" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>כלל תמר שקלים</t>
+          <t>קופת התגמולים לעובדי האוניברסיטה העברית בירושלים בע"מ עד 50</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>43.7</v>
       </c>
       <c r="G182" t="n">
-        <v>174</v>
+        <v>121</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>להבה מסלול שקלי</t>
+          <t>קופת תגמולים  עיריית חיפה מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F183" t="n">
-        <v>0</v>
-      </c>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>להיט קופה לתגמולים ופיצויים מסלול שקלי</t>
+          <t>קופת תגמולים של העובדים בעירית תל אביב- יפו אגודה שיתופית בע"מ מסלול לבני 50 ומטה.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr"/>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>48.1</v>
+      </c>
       <c r="G184" t="n">
-        <v>12</v>
+        <v>121</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>מגדל השתלמות מסלול מט"ח</t>
+          <t>רשף - מסלול לבני 50 ומטה</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="G185" t="n">
-        <v>51</v>
+        <v>110</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>מיטב גאון גמל-מסלול מט"ח</t>
+          <t>שובל -  קופת גמל ענפית עד 50</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>8.1</v>
+        <v>50</v>
       </c>
       <c r="G186" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>מיטב גאון השתלמות מסלולית-מסלול מט"ח</t>
+          <t>תגמולים של העובדים בעיריית תל אביב - יפו אגודה שיתופית בע"מ עד 50</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>מדרגות</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>עד 50</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>כספי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="F187" t="n">
-        <v>0</v>
-      </c>
+          <t>בינונית</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>מיטב דינאמית גמל מסלול שקלי</t>
+          <t>איילון השתלמות מסלול מט"ח</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -6584,13 +6598,13 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>מיטב דינאמית להשתלמות מסלול שקלי</t>
+          <t>איילון השתלמות מסלול שקלי</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6617,23 +6631,23 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>מיטב דש השתלמות מסלול שקלי</t>
+          <t>איילון לפיצויים מסלול מט"ח</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -6646,27 +6660,25 @@
           <t>נמוכה</t>
         </is>
       </c>
-      <c r="F190" t="n">
-        <v>0</v>
-      </c>
+      <c r="F190" t="inlineStr"/>
       <c r="G190" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>מיטב מרום מסלול מט"ח</t>
+          <t>איילון לפיצויים מסלול שקלי</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6679,27 +6691,25 @@
           <t>נמוכה</t>
         </is>
       </c>
-      <c r="F191" t="n">
-        <v>0</v>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>מיטב פיצויים שקלי</t>
+          <t>איילון תגמולים ואישית לפיצויים מסלול מט"ח</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -6716,23 +6726,23 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>180</v>
+        <v>41</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>מנורה מסד השתלמות - מסלול מט"חי</t>
+          <t>איילון תגמולים ואישית לפיצויים מסלול שקלי</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -6745,25 +6755,27 @@
           <t>נמוכה</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
       <c r="G193" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>פסגות גדיש שקלית</t>
+          <t>אנליסט גמל מט"ח</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -6786,17 +6798,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>קופת התגמולים לעובדים האקדמאים של אוניברסיטת תל אביב - מסלול שקלי</t>
+          <t>אקסלנס אופיר - מסלול מט"ח טווח קצר</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>מט"ח טווח קצר</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -6813,23 +6825,23 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>קרן השתלמות נירית שקלי</t>
+          <t>אקסלנס גמל מט"ח</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>שיקלי</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>שקלי</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -6842,25 +6854,27 @@
           <t>נמוכה</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
+      <c r="F196" t="n">
+        <v>92.40000000000001</v>
+      </c>
       <c r="G196" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>תגב - מט"ח דולרי</t>
+          <t>אקסלנס גמל פלטינום שקלי</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>מט"ח</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>מט"ח דולרי</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -6873,169 +6887,171 @@
           <t>נמוכה</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
       <c r="G197" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>אגודה שיתופית של עובדי התעשיה האוירית לניהול קופות גמל בע"מ מסלול לבני 50 ומטה</t>
+          <t>אקסלנס גמל שקלי</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>77.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>121</v>
+        <v>62</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>אדמונד דה רוטשילד דיסקונט חו"ל</t>
+          <t>אקסלנס השתלמות מט"ח</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>35.8</v>
+        <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>אופיר מסלול חו"ל</t>
+          <t>אקסלנס השתלמות פלטינום שקלי</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr"/>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
       <c r="G200" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>אי.בי.אי. לתגמולים ופיצויים מסלול לבני 50 ומטה</t>
+          <t>אקסלנס השתלמותשקלי</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F201" t="n">
-        <v>42.3</v>
-      </c>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
       <c r="G201" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>איילון השתלמות מסלול חו"ל</t>
+          <t>אקסלנס משכית - מסלול מט"ח טווח קצר</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מט"ח טווח קצר</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>33.7</v>
+        <v>0</v>
       </c>
       <c r="G202" t="n">
         <v>18</v>
@@ -7044,976 +7060,970 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>איילון תגמולים ואישית לפיצויים מסלול חו"ל</t>
+          <t>אקסלנס משכית - מסלול מט"חי</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>איילון תגמולים ואישית לפיצויים מסלולית עד 50</t>
+          <t>אקסלנס עדי - מסלול מט"ח טווח קצר</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מט"ח טווח קצר</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>אינפיניטי גמל מסלול לבני 50 ומטה</t>
+          <t>אקסלנס שחקים מסלול שקלי ב'</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>50.9</v>
+        <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>121</v>
+        <v>13</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>אלטשולר שחם גמל לבני 50 ומטה</t>
+          <t>אתגרים - מסלול שיקלי</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F206" t="n">
-        <v>52.5</v>
-      </c>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>121</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>אלטשולר שחם גמל לעמיתי חבר עד 50</t>
+          <t>אתגרים לפיצויים - מסלול שיקלי</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F207" t="n">
-        <v>53</v>
-      </c>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>122</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>אלפא מור קופת גמל לחיסכון, קופת גמל לתגמולים וקופת גמל אישית לפיצויים - לבני 50 ומטה</t>
+          <t>הלמן-אלדובי בר-יציב שקלי</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>56.6</v>
+        <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>85</v>
+        <v>108</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>אנליסט מסלולית קופת גמל - מסלול לבני 50 ומטה</t>
+          <t>הלמן-אלדובי השתלמות שקלי</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>53.9</v>
+        <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>אנליסט מסלולית קופת גמל ישראל</t>
+          <t>הפניקס מרכזית לפיצויים שקלי</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="G210" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>אקסלנס גמל זהב חו"ל</t>
+          <t>הראל גמל מסלול שקלי</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr"/>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
       <c r="G211" t="n">
-        <v>15</v>
+        <v>115</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>אקסלנס גמל חו"ל</t>
+          <t>הראל השתלמות מסלול שקלי</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr"/>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
       <c r="G212" t="n">
-        <v>43</v>
+        <v>115</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>אקסלנס השתלמות זהב חו"ל</t>
+          <t>הראל קמ"פ מסלול שקלי</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr"/>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
       <c r="G213" t="n">
-        <v>15</v>
+        <v>132</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>אקסלנס השתלמות חו"ל</t>
+          <t>חיננית - מסלול מט"ח</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr"/>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
       <c r="G214" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ארם - קופת גמל לתגמולים של ארגון הרופאים עובדי המדינה עד 50</t>
+          <t>חיננית - מסלול שקלי</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>121</v>
+        <v>13</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>גמל-על, קופת תגמולים לעובדי אל על, אגודה שיתופית בע"מ עד 50</t>
+          <t>כלל גמל מט"ח</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F216" t="n">
-        <v>54.3</v>
-      </c>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>122</v>
+        <v>4</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>דש אקונומיסט השתלמות חו"ל</t>
+          <t>כלל גמל שקלי</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F217" t="n">
-        <v>31.7</v>
-      </c>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>דש תגמולים חו"ל</t>
+          <t>כלל השתלמות מט"ח</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F218" t="n">
-        <v>31.8</v>
-      </c>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
-        <v>12</v>
+        <v>74</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>הילה - לבני 50 ומטה</t>
+          <t>כלל השתלמות שקלים</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F219" t="n">
-        <v>46.7</v>
-      </c>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="n">
-        <v>110</v>
+        <v>74</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>הלמן-אלדובי בר-יציב חו"ל</t>
+          <t>כלל תמר מט"ח</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>37.7</v>
+        <v>0.9</v>
       </c>
       <c r="G220" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>הלמן-אלדובי גמל ישראל</t>
+          <t>כלל תמר שקלים</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>33.8</v>
+        <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>142</v>
+        <v>174</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>הלמן-אלדובי גמל מסלול לבני 50 ומטה</t>
+          <t>להבה מסלול שקלי</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>הלמן-אלדובי השתלמות חו"ל</t>
+          <t>להיט קופה לתגמולים ופיצויים מסלול שקלי</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F223" t="n">
-        <v>37.8</v>
-      </c>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
       <c r="G223" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>הלמן-אלדובי השתלמות ישראל</t>
+          <t>מגדל השתלמות מסלול מט"ח</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>ישראל</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>34.4</v>
+        <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>הפניקס גמל חו"ל</t>
+          <t>מיטב גאון גמל-מסלול מט"ח</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>37.7</v>
+        <v>8.1</v>
       </c>
       <c r="G225" t="n">
-        <v>79</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>הפניקס גמל לבני 50 ומטה</t>
+          <t>מיטב גאון השתלמות מסלולית-מסלול מט"ח</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>121</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>הפניקס גמל פאסיבי לבני 50 ומטה</t>
+          <t>מיטב דינאמית גמל מסלול שקלי</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>49.2</v>
+        <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>104</v>
+        <v>27</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>הפניקס תגמולים ופיצויים - מסלול לבני 50 ומטה</t>
+          <t>מיטב דינאמית להשתלמות מסלול שקלי</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>33.4</v>
+        <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>הראל גמל לגילאי 50 ומטה</t>
+          <t>מיטב דש השתלמות מסלול שקלי</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>35.1</v>
+        <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>הראל גמל מסלול לגילאי  50 ומטה</t>
+          <t>מיטב מרום מסלול מט"ח</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>49.8</v>
+        <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>121</v>
+        <v>43</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>הראל גמל מסלול- חו"ל</t>
+          <t>מיטב פיצויים שקלי</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>34.7</v>
+        <v>0</v>
       </c>
       <c r="G231" t="n">
-        <v>78</v>
+        <v>180</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>חברה לניהול קופות גמל של העובדים בעיריית תל - אביב יפו בע"מ עד 50</t>
+          <t>מנורה מסד השתלמות - מסלול מט"חי</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -8024,434 +8034,432 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ילין לפידות קופת גמל מסלול לבני 50 ומטה</t>
+          <t>פסגות גדיש שקלית</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>52.5</v>
+        <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>121</v>
+        <v>72</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>כור-תדיראן קופת גמל אישית לתגמולים ולפיצויים עד 50</t>
+          <t>קופת התגמולים לעובדים האקדמאים של אוניברסיטת תל אביב - מסלול שקלי</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>כלל גמל חו"ל</t>
+          <t>קרן השתלמות נירית שקלי</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>שיקלי</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>שקלי</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>כלל תמר עד 50</t>
+          <t>תגב - מט"ח דולרי</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מט"ח</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מט"ח דולרי</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כספי</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-      <c r="F236" t="n">
-        <v>48.1</v>
-      </c>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>122</v>
+        <v>9</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>מגדל גמל להשקעה חו"ל</t>
+          <t>בר קרן גמולים א' - מבטיח תשואה בשיעור 5.5 אחוז לשנה</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>34.4</v>
+        <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>מגדל השתלמות מסלול חו"ל</t>
+          <t>הפניקס גמולה מבטיחת תשואה</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>33.9</v>
+        <v>1.3</v>
       </c>
       <c r="G238" t="n">
-        <v>153</v>
+        <v>181</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>מגדל השתלמות מסלול לבני 50 ומטה</t>
+          <t>מיטב ביטחון מבטיח תשואה 4.5%</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>מתמחה אחר</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>אוכלוסיית יעד</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>44.9</v>
+        <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>93</v>
+        <v>192</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>מגדל לתגמולים ולפיצויים מסלול חו"ל</t>
+          <t>מיטב ביטחון מבטיח תשואה 5.5%</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ללא סיווג</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>33.6</v>
+        <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>153</v>
+        <v>192</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>מגדל לתגמולים ולפיצויים מסלול לבני 50 ומטה</t>
+          <t>מנורה מבטחים אמיר מדד בגין</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>50.1</v>
+        <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>122</v>
+        <v>192</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>מור מנורה מבטחים מסלול לבני 50 ומטה</t>
+          <t>מנורה מבטחים אמיר מדד ידוע</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>49.1</v>
+        <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>123</v>
+        <v>192</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>מחוג  מסלול לבני 50 ומטה</t>
+          <t>מנורה מבטחים יותר מסלול א'</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>48.4</v>
+        <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>121</v>
+        <v>192</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>מיטב אגוד תגמולים עד 50</t>
+          <t>מנורה מבטחים יותר מסלול ב'</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F244" t="n">
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>105</v>
+        <v>192</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>מיטב גמל לבני 50 ומטה</t>
+          <t>מנורה מבטחים יותר מסלול ג'</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>121</v>
+        <v>192</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>מיטב דש גמל חו"ל</t>
+          <t>אדמונד דה רוטשילד דיסקונט חו"ל</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -8475,16 +8483,16 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>35.1</v>
+        <v>35.8</v>
       </c>
       <c r="G246" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>מיטב דש השתלמות חו"ל</t>
+          <t>אופיר מסלול חו"ל</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -8507,27 +8515,25 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F247" t="n">
-        <v>34.8</v>
-      </c>
+      <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>מנורה מבטחים תגמולים ופיצויים מסלול לבני 50 ומטה</t>
+          <t>איילון השתלמות מסלול חו"ל</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -8541,16 +8547,16 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>48.6</v>
+        <v>33.7</v>
       </c>
       <c r="G248" t="n">
-        <v>123</v>
+        <v>18</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>משכית מסלול חו"ל</t>
+          <t>איילון תגמולים ואישית לפיצויים מסלול חו"ל</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -8573,25 +8579,27 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr"/>
+      <c r="F249" t="n">
+        <v>34.5</v>
+      </c>
       <c r="G249" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>סלייס גמל קופת גמל לחסכון חו"ל חו"ל</t>
+          <t>אנליסט מסלולית קופת גמל ישראל</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>ישראל</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>ישראל</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -8605,26 +8613,26 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>60.1</v>
+        <v>45.5</v>
       </c>
       <c r="G250" t="n">
-        <v>93</v>
+        <v>174</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>סלייס גמל קופת גמל לחסכון מדרגות עד 50</t>
+          <t>אקסלנס גמל זהב חו"ל</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -8637,22 +8645,20 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F251" t="n">
-        <v>62.2</v>
-      </c>
+      <c r="F251" t="inlineStr"/>
       <c r="G251" t="n">
-        <v>93</v>
+        <v>15</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>סלייס השתלמות חו"ל חו"ל</t>
+          <t>אקסלנס גמל חו"ל</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8672,23 +8678,23 @@
       </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>עוצ"מ - אגודה שיתופית לניהול קופות גמל בע"מ - מסלול לבני 50 ומטה</t>
+          <t>אקסלנס השתלמות זהב חו"ל</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -8701,29 +8707,27 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F253" t="n">
-        <v>47.9</v>
-      </c>
+      <c r="F253" t="inlineStr"/>
       <c r="G253" t="n">
-        <v>123</v>
+        <v>15</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>פסגות NEXT גמל להשקעה חו"ל</t>
+          <t>אקסלנס השתלמות חו"ל</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
+          <t>ללא סיווג</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
           <t>חו"ל</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>חו"ל</t>
-        </is>
-      </c>
       <c r="D254" t="inlineStr">
         <is>
           <t>מניות אקטיבי</t>
@@ -8734,17 +8738,15 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F254" t="n">
-        <v>35</v>
-      </c>
+      <c r="F254" t="inlineStr"/>
       <c r="G254" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>פסגות גדיש חו"ל</t>
+          <t>דש אקונומיסט השתלמות חו"ל</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8768,26 +8770,26 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>33.1</v>
+        <v>31.7</v>
       </c>
       <c r="G255" t="n">
-        <v>142</v>
+        <v>12</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>פסגות גדיש לבני 50  ומטה</t>
+          <t>דש תגמולים חו"ל</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -8801,16 +8803,16 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>45.2</v>
+        <v>31.8</v>
       </c>
       <c r="G256" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>פסגות שיא השתלמות חו"ל</t>
+          <t>הלמן-אלדובי בר-יציב חו"ל</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8834,16 +8836,16 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>34.7</v>
+        <v>37.7</v>
       </c>
       <c r="G257" t="n">
-        <v>105</v>
+        <v>37</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>פסגות שיא השתלמות ישראל</t>
+          <t>הלמן-אלדובי גמל ישראל</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8867,7 +8869,7 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>33.5</v>
+        <v>33.8</v>
       </c>
       <c r="G258" t="n">
         <v>142</v>
@@ -8876,17 +8878,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>קו הבריאות קופת גמל לתגמולים ולפיצויים (לא משלמת) לבני 50 ומטה</t>
+          <t>הלמן-אלדובי השתלמות חו"ל</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -8900,26 +8902,26 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>51.8</v>
+        <v>37.8</v>
       </c>
       <c r="G259" t="n">
-        <v>121</v>
+        <v>37</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>קופת גמל אישית לפיצויים של העובדים בעיריית תל-אביב יפו - מסלול לבני 50 ומטה</t>
+          <t>הלמן-אלדובי השתלמות ישראל</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ישראל</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>ישראל</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -8933,26 +8935,26 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>34.4</v>
       </c>
       <c r="G260" t="n">
-        <v>104</v>
+        <v>37</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>קופת גמל גל לבני 50 ומטה</t>
+          <t>הפניקס גמל חו"ל</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -8966,26 +8968,26 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>51.5</v>
+        <v>37.7</v>
       </c>
       <c r="G261" t="n">
-        <v>121</v>
+        <v>79</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>קופת גמל הגומל לבני 50 ומטה</t>
+          <t>הראל גמל מסלול- חו"ל</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -8999,26 +9001,26 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>49.2</v>
+        <v>34.7</v>
       </c>
       <c r="G262" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>קופת גמל הנדסאים - מסלול עד 50</t>
+          <t>כלל גמל חו"ל</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -9031,27 +9033,25 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F263" t="n">
-        <v>48.5</v>
-      </c>
+      <c r="F263" t="inlineStr"/>
       <c r="G263" t="n">
-        <v>122</v>
+        <v>4</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>קופת גמל כלנית לבני 50 ומטה</t>
+          <t>מגדל גמל להשקעה חו"ל</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -9065,26 +9065,26 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>51.3</v>
+        <v>34.4</v>
       </c>
       <c r="G264" t="n">
-        <v>122</v>
+        <v>92</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>קופת גמל למשרתי הקבע בצה"ל קופת גמל לא משלמת לקצבה עד 50</t>
+          <t>מגדל השתלמות מסלול חו"ל</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -9098,26 +9098,26 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>42.9</v>
+        <v>33.9</v>
       </c>
       <c r="G265" t="n">
-        <v>63</v>
+        <v>153</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>קופת גמל מחר לבני 50 ומטה</t>
+          <t>מגדל לתגמולים ולפיצויים מסלול חו"ל</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -9131,26 +9131,26 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>41.2</v>
+        <v>33.6</v>
       </c>
       <c r="G266" t="n">
-        <v>122</v>
+        <v>153</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>קופת גמל עו"ס לבני 50 ומטה</t>
+          <t>מיטב דש גמל חו"ל</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -9164,26 +9164,26 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>48.6</v>
+        <v>35.1</v>
       </c>
       <c r="G267" t="n">
-        <v>122</v>
+        <v>85</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>קופת גמל עמ"י מסלול לבני 50 ומטה</t>
+          <t>מיטב דש השתלמות חו"ל</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -9197,26 +9197,26 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>50.9</v>
+        <v>34.8</v>
       </c>
       <c r="G268" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>קופת גמל שדות לבני 50 ומטה</t>
+          <t>משכית מסלול חו"ל</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -9229,27 +9229,25 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F269" t="n">
-        <v>43.5</v>
-      </c>
+      <c r="F269" t="inlineStr"/>
       <c r="G269" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>קופת התגמולים לעובדי בנק דיסקונט לבני  50 ומטה</t>
+          <t>סלייס גמל קופת גמל לחסכון חו"ל חו"ל</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -9263,26 +9261,26 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>58</v>
+        <v>60.1</v>
       </c>
       <c r="G270" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>קופת התגמולים לעובדי האוניברסיטה העברית בירושלים בע"מ עד 50</t>
+          <t>סלייס השתלמות חו"ל חו"ל</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -9295,27 +9293,25 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F271" t="n">
-        <v>43.7</v>
-      </c>
+      <c r="F271" t="inlineStr"/>
       <c r="G271" t="n">
-        <v>121</v>
+        <v>86</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>קופת תגמולים  עיריית חיפה מסלול לבני 50 ומטה</t>
+          <t>פסגות NEXT גמל להשקעה חו"ל</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -9328,25 +9324,27 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr"/>
+      <c r="F272" t="n">
+        <v>35</v>
+      </c>
       <c r="G272" t="n">
-        <v>103</v>
+        <v>60</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>קופת תגמולים של העובדים בעירית תל אביב- יפו אגודה שיתופית בע"מ מסלול לבני 50 ומטה.</t>
+          <t>פסגות גדיש חו"ל</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -9360,26 +9358,26 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>48.1</v>
+        <v>33.1</v>
       </c>
       <c r="G273" t="n">
-        <v>121</v>
+        <v>142</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>רשף - מסלול לבני 50 ומטה</t>
+          <t>פסגות שיא השתלמות חו"ל</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ללא סיווג</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -9393,26 +9391,26 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>46.7</v>
+        <v>34.7</v>
       </c>
       <c r="G274" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>שובל -  קופת גמל ענפית עד 50</t>
+          <t>פסגות שיא השתלמות ישראל</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>ישראל</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>ישראל</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -9426,31 +9424,31 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>50</v>
+        <v>33.5</v>
       </c>
       <c r="G275" t="n">
-        <v>63</v>
+        <v>142</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>תגמולים של העובדים בעיריית תל אביב - יפו אגודה שיתופית בע"מ עד 50</t>
+          <t>אי.בי.אי השתלמות מסלול מחקה מדד STOXX EUROPE 600</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>מדרגות</t>
+          <t>מדד</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>עד 50</t>
+          <t>מדד</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>מניות פאסיבי</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -9460,13 +9458,13 @@
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>אי.בי.אי השתלמות מסלול מחקה מדד STOXX EUROPE 600</t>
+          <t>אי.בי.אי לתגמולים ופיצויים מסלול מחקה מדד STOXX EUROPE 600</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -9491,23 +9489,23 @@
       </c>
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>אי.בי.אי לתגמולים ופיצויים מסלול מחקה מדד STOXX EUROPE 600</t>
+          <t>אקסלנס השתלמות פאסיבי- מדדי חו"ל</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>מדד</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>מדד</t>
+          <t>פאסיבי</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -9520,27 +9518,29 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr"/>
+      <c r="F278" t="n">
+        <v>40.4</v>
+      </c>
       <c r="G278" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>אקסלנס השתלמות פאסיבי- מדדי חו"ל</t>
+          <t>סלייס גמל קופת גמל לחסכון מדד חו"ל</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
+          <t>מדד</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
           <t>חו"ל</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>פאסיבי</t>
-        </is>
-      </c>
       <c r="D279" t="inlineStr">
         <is>
           <t>מניות פאסיבי</t>
@@ -9552,26 +9552,26 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>40.4</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="G279" t="n">
-        <v>26</v>
+        <v>93</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>סלייס גמל קופת גמל לחסכון מדד חו"ל</t>
+          <t>סלייס השתלמות חו"ל פאסיבי</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>מדד</t>
+          <t>חו"ל</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>פאסיבי</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -9584,29 +9584,27 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F280" t="n">
-        <v>95.40000000000001</v>
-      </c>
+      <c r="F280" t="inlineStr"/>
       <c r="G280" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>סלייס השתלמות חו"ל פאסיבי</t>
+          <t>סלייס השתלמות מדד חו"ל</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
+          <t>מדד</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
           <t>חו"ל</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>פאסיבי</t>
-        </is>
-      </c>
       <c r="D281" t="inlineStr">
         <is>
           <t>מניות פאסיבי</t>
@@ -9617,15 +9615,17 @@
           <t>גבוהה</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr"/>
+      <c r="F281" t="n">
+        <v>97.09999999999999</v>
+      </c>
       <c r="G281" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>סלייס השתלמות מדד חו"ל</t>
+          <t>סלייס קופת גמל להשקעה מדד חו"ל</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -9649,75 +9649,42 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>97.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="G282" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>סלייס קופת גמל להשקעה מדד חו"ל</t>
+          <t>אלטשולר שחם גמל עוקב מדדים- גמיש</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>מדד</t>
+          <t>(ריק)</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>חו"ל</t>
+          <t>(ריק)</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>מניות פאסיבי</t>
+          <t>מעורב / גמיש</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>97.5</v>
+        <v>49.1</v>
       </c>
       <c r="G283" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>אלטשולר שחם גמל עוקב מדדים- גמיש</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>(ריק)</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>(ריק)</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>מעורב / גמיש</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-      <c r="F284" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="G284" t="n">
         <v>37</v>
       </c>
     </row>
@@ -9732,7 +9699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9775,15 +9742,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>מניות אקטיבי</t>
+          <t>כללי</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>בינונית</t>
         </is>
       </c>
     </row>
@@ -9805,88 +9772,73 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>אג"ח ממשלתי</t>
+          <t>מניות אקטיבי</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>נמוכה</t>
+          <t>גבוהה</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>אג"ח עד 25% מניות</t>
+          <t>מבטיח תשואה</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>בינונית</t>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>מניות פאסיבי</t>
+          <t>אג"ח עד 25% מניות</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>בינונית</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>כללי</t>
+          <t>מניות פאסיבי</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>בינונית</t>
+          <t>גבוהה</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>אחר, לבדיקה</t>
+          <t>מעורב / גמיש</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>מעורב / גמיש</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>בינונית</t>
         </is>
